--- a/data/trans_orig/P6607-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48150</t>
+          <t>48819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72133</t>
+          <t>71803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58799</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76243</t>
+          <t>76977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114307</t>
+          <t>113931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144708</t>
+          <t>144705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34814</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50616</t>
+          <t>49342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25567</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>35892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>42669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>46931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>71670</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>70585</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93897</t>
+          <t>92879</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>124132</t>
+          <t>122382</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>159435</t>
+          <t>158343</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39911</t>
+          <t>40341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>33431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40657</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67247</t>
+          <t>66718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45755</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>26578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53286</t>
+          <t>52409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65002</t>
+          <t>64026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49103</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79532</t>
+          <t>79221</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>33704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55267</t>
+          <t>55903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>52613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69151</t>
+          <t>68414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121016</t>
+          <t>119133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51560</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63308</t>
+          <t>61135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42692</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>50812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36311</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36774</t>
+          <t>36788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61363</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>66257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85207</t>
+          <t>85368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107972</t>
+          <t>108044</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140451</t>
+          <t>139490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33414</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>29124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58409</t>
+          <t>57280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>24212</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>47911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>54113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37169</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34969</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47726</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57375</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81561</t>
+          <t>81523</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>28084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33235</t>
+          <t>33979</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38318</t>
+          <t>37666</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55665</t>
+          <t>56198</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28296</t>
+          <t>29062</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>43419</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66260</t>
+          <t>66261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94244</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42815</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32582</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56043</t>
+          <t>57395</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28188</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31875</t>
+          <t>33279</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>34005</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>39760</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>101181</t>
+          <t>104002</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>136041</t>
+          <t>135644</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>119562</t>
+          <t>120247</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>145104</t>
+          <t>144367</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>228629</t>
+          <t>230364</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>272190</t>
+          <t>272498</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>74936</t>
+          <t>74184</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>38051</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>69852</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>106078</t>
+          <t>104336</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>63407</t>
+          <t>62617</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>49521</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>79639</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>56412</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>37208</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>63334</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>154738</t>
+          <t>155635</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>194756</t>
+          <t>194195</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>173784</t>
+          <t>174160</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>204269</t>
+          <t>203148</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>340850</t>
+          <t>339978</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>390057</t>
+          <t>389974</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>56174</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>86294</t>
+          <t>87261</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>50802</t>
+          <t>51323</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>89011</t>
+          <t>88713</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>129272</t>
+          <t>126519</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>57482</t>
+          <t>56685</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>88776</t>
+          <t>88712</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>72498</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>107346</t>
+          <t>108201</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>31063</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>57892</t>
+          <t>56328</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45037</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>75169</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>539460</t>
+          <t>540046</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>613819</t>
+          <t>615807</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>661766</t>
+          <t>659481</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>718364</t>
+          <t>716899</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1214727</t>
+          <t>1216760</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1317617</t>
+          <t>1316405</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>266271</t>
+          <t>268030</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>332619</t>
+          <t>332366</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>130074</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>176825</t>
+          <t>175282</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>410354</t>
+          <t>410417</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>489697</t>
+          <t>488004</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>231578</t>
+          <t>234360</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>291893</t>
+          <t>293645</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>68036</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>279821</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>347372</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>246765</t>
+          <t>244837</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>304392</t>
+          <t>307204</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>70279</t>
+          <t>69093</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>292255</t>
+          <t>289413</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>362058</t>
+          <t>360075</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>54901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66355</t>
+          <t>66894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84628</t>
+          <t>84702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102540</t>
+          <t>101160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132334</t>
+          <t>134075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56007</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71365</t>
+          <t>71960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34487</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46194</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70457</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61393</t>
+          <t>62603</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82924</t>
+          <t>83012</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>114086</t>
+          <t>111514</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>148283</t>
+          <t>146438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49515</t>
+          <t>49035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>43510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>31217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37381</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40888</t>
+          <t>41688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66509</t>
+          <t>67231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>25849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55640</t>
+          <t>56401</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86011</t>
+          <t>86765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60681</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>92855</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119484</t>
+          <t>119274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22597</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>57898</t>
+          <t>57957</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35079</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37138</t>
+          <t>35585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47070</t>
+          <t>47159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53185</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>68183</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85101</t>
+          <t>84255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112150</t>
+          <t>114526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32869</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>46406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13434</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>16706</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34765</t>
+          <t>35119</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42153</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41504</t>
+          <t>41311</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>46035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>67505</t>
+          <t>68100</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>26780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36880</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29594</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>41562</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45084</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60173</t>
+          <t>60236</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71726</t>
+          <t>71890</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>88182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>115922</t>
+          <t>115257</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>115870</t>
+          <t>117043</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>156078</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>148449</t>
+          <t>150142</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>181775</t>
+          <t>182853</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>276872</t>
+          <t>276458</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>328289</t>
+          <t>329190</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>108653</t>
+          <t>109365</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>148884</t>
+          <t>147256</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69513</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>102617</t>
+          <t>101133</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>186094</t>
+          <t>186802</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>236490</t>
+          <t>235819</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64159</t>
+          <t>63552</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>60299</t>
+          <t>60042</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>93221</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>33804</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37288</t>
+          <t>39481</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>65892</t>
+          <t>67830</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>151175</t>
+          <t>147196</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>185886</t>
+          <t>185415</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>168148</t>
+          <t>169509</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>195404</t>
+          <t>196392</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>327928</t>
+          <t>327357</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>373337</t>
+          <t>372946</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>51401</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>80589</t>
+          <t>80256</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>82581</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>118972</t>
+          <t>119517</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>65853</t>
+          <t>63599</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25263</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>51963</t>
+          <t>51348</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>82677</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>54529</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37699</t>
+          <t>37571</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>65187</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>506671</t>
+          <t>508040</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>584108</t>
+          <t>581427</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>689865</t>
+          <t>690314</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>746907</t>
+          <t>748661</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1214293</t>
+          <t>1216608</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1308733</t>
+          <t>1316116</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>325486</t>
+          <t>328787</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>396758</t>
+          <t>395988</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>219304</t>
+          <t>219340</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>511582</t>
+          <t>516810</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>595566</t>
+          <t>599167</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>199267</t>
+          <t>201614</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>259207</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>259230</t>
+          <t>260269</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>324161</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>247712</t>
+          <t>248389</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>311315</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>75326</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>302003</t>
+          <t>302411</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>369739</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53374</t>
+          <t>52899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>51073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60467</t>
+          <t>60548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>82868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111625</t>
+          <t>111186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49750</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37885</t>
+          <t>37729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60665</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>26041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47726</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63537</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78059</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107114</t>
+          <t>108689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>41954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>44939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28366</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>25342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>39243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>41978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63662</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27212</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>52527</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18562</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>24338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27064</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72620</t>
+          <t>72462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91471</t>
+          <t>91706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>68713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152130</t>
+          <t>150038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103610</t>
+          <t>111828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>23176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53580</t>
+          <t>54028</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13807,12 +13807,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15763</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13920,12 +13920,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37774</t>
+          <t>37222</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54081</t>
+          <t>51874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74047</t>
+          <t>72600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>78054</t>
+          <t>77207</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>103754</t>
+          <t>104023</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>103463</t>
+          <t>103874</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>119715</t>
+          <t>119701</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>185823</t>
+          <t>186439</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>218811</t>
+          <t>219417</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>54013</t>
+          <t>55434</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>38940</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>48629</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>166946</t>
+          <t>166682</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>73109</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>92593</t>
+          <t>93320</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>274785</t>
+          <t>274854</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>122923</t>
+          <t>121485</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38275</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>146524</t>
+          <t>147163</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>96484</t>
+          <t>96279</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>102620</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>84011</t>
+          <t>86990</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>402365</t>
+          <t>404052</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>81749</t>
+          <t>83939</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>482108</t>
+          <t>488106</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>208745</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>483755</t>
+          <t>483375</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>393808</t>
+          <t>365120</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>498104</t>
+          <t>498252</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>539710</t>
+          <t>552664</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>981182</t>
+          <t>990896</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>113770</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>279186</t>
+          <t>279671</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>104829</t>
+          <t>101706</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>225167</t>
+          <t>245332</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>227840</t>
+          <t>224103</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>429608</t>
+          <t>439479</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>73875</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>179885</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>105177</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>207605</t>
+          <t>209816</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>193167</t>
+          <t>193105</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>741629</t>
+          <t>695128</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>223928</t>
+          <t>221107</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>911621</t>
+          <t>918309</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
